--- a/import_templates/06_Budget_Finanziario.xlsx
+++ b/import_templates/06_Budget_Finanziario.xlsx
@@ -222,7 +222,7 @@
       <text>
         <t>Riga: conto contabile
 [OBBLIGATORIO]
-Formato: 4101
+Formato: 3101
 Codice del conto del piano dei conti (deve esistere).</t>
       </text>
     </comment>
@@ -592,7 +592,7 @@
       <c r="C2" s="3" t="inlineStr"/>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -610,7 +610,7 @@
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -628,7 +628,7 @@
       <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -646,7 +646,7 @@
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -2525,7 +2525,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2573,7 +2573,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
